--- a/hydration/samples/2_purchase_orders.xlsx
+++ b/hydration/samples/2_purchase_orders.xlsx
@@ -489,7 +489,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PO_001</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
